--- a/assets/SciClaimEval26_Results.xlsx
+++ b/assets/SciClaimEval26_Results.xlsx
@@ -5,36 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\AGP_NAS_DS923\home\05_Projects\02_Academics\NTCIR_ClaimVerification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\andreg-p\work\sciclaimeval.github.io\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401A2B50-BF19-4AF7-ACAA-6D6859693DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8066E1F4-6499-4EF7-BEFF-79184E034657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="1335" windowWidth="29310" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="2100" windowWidth="33165" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run Evaluations" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="578">
   <si>
     <t>run_id</t>
   </si>
@@ -1637,6 +1623,117 @@
     <t>Comparing contexts from different evidence types</t>
   </si>
   <si>
+    <t>97769c6b10ccd66e09c1a8b65359de32</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-m3q-Y_wNk8cUzo6p4ZOPpzcLJmd8EoO</t>
+  </si>
+  <si>
+    <t>Qwen3-VL-32B-Instruct + fine-tuning + prompting</t>
+  </si>
+  <si>
+    <t>Step-by-step reasoning prompt to support the model used for SIBTM_T2_R03</t>
+  </si>
+  <si>
+    <t>92876017b01d1bb6a165965de6a98ee5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_cS9uZWYFuWpFrLzgc6PxDqzVx3cH05J</t>
+  </si>
+  <si>
+    <t>b6729d09d9a2903c068d050361a093c3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1sxW31y3ioo-l9v1XSI4EDBu8LcJzR7dh</t>
+  </si>
+  <si>
+    <t>4607840199d0961418033b806c091fa5</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1NtlFDMD0zO9DEv0zSfnDvEan__Jq_KsV</t>
+  </si>
+  <si>
+    <t>QLoRA fine-tuning of Qwen3 on automatically-perturbed claim-evidence pairs derived from SIBiLS/PMC OA tables and figures</t>
+  </si>
+  <si>
+    <t>6607f586a28e28900dc37020cf21d625</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xP-Ybn31kaGQDS9Dts8ve2vsuRnFp_XS</t>
+  </si>
+  <si>
+    <t>Qwen3-VL decider + chart/table advisor</t>
+  </si>
+  <si>
+    <t>ChartGemma and PaddleOCR act as advisors, extracting figure interpretations and table structure respectively, which Qwen uses to make the final decision</t>
+  </si>
+  <si>
+    <t>ddcfd68c99ae727089638c31c1da07e2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1y049nj1HHxdpPPPWaDQAnBs8WVJKGciL</t>
+  </si>
+  <si>
+    <t>subtask1-one-stage-thinking</t>
+  </si>
+  <si>
+    <t>cdbdf8cdaec530a81de30d0fa3927443</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1_ygoFIGlit7gBAQYmghQt3M7IoMxu8vh</t>
+  </si>
+  <si>
+    <t>v8</t>
+  </si>
+  <si>
+    <t>eaba2ac274b0c606725e764419e82552</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1AckeyWWuawlutcZ0fWoiBgoztRfK-h4Z</t>
+  </si>
+  <si>
+    <t>CommitID: bf1bce5</t>
+  </si>
+  <si>
+    <t>69130f5806bb87851690bd623f6d70d8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1i3tMkTIF_QTWJq3VG0yoGGORFqMTNcMH</t>
+  </si>
+  <si>
+    <t>v9</t>
+  </si>
+  <si>
+    <t>249d7a0e5ad4877a57d3aefcb669a930</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=17LmdOBudHSa6GO3wheBfrjr8XHlpkRxD</t>
+  </si>
+  <si>
+    <t>2e2e8b28fa20c0070ca9d592d494e5b4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1nlgWtXlR1uLHnp7qICMq7iahRBulMMqh</t>
+  </si>
+  <si>
+    <t>daf1d60cb0b82a5747733a605efc11f1</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-8WT9MlOcG62Da6L9_Yn2PduZ41N10Yd</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>c8a371d1baa6f2934ea62d457c24dc79</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1av4H2wf4z-oDnmR3wUAgFXGBW3nT1mTM</t>
+  </si>
+  <si>
+    <t>image input + CoT + pairwise inference + gemma4 31b none thinking</t>
+  </si>
+  <si>
     <t>5cd8ec8f43a1983a1595f9cbc8d38ba7</t>
   </si>
   <si>
@@ -1652,73 +1749,6 @@
     <t>baseline_phi4_qwenvl</t>
   </si>
   <si>
-    <t>Unable to identify participant e-mails.
-Exception: "Unable to match Group ID 'CAISA26' or Group Name 'CAISALab'"</t>
-  </si>
-  <si>
-    <t>97769c6b10ccd66e09c1a8b65359de32</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1-m3q-Y_wNk8cUzo6p4ZOPpzcLJmd8EoO</t>
-  </si>
-  <si>
-    <t>Qwen3-VL-32B-Instruct + fine-tuning + prompting</t>
-  </si>
-  <si>
-    <t>Step-by-step reasoning prompt to support the model used for SIBTM_T2_R03</t>
-  </si>
-  <si>
-    <t>92876017b01d1bb6a165965de6a98ee5</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1_cS9uZWYFuWpFrLzgc6PxDqzVx3cH05J</t>
-  </si>
-  <si>
-    <t>b6729d09d9a2903c068d050361a093c3</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1sxW31y3ioo-l9v1XSI4EDBu8LcJzR7dh</t>
-  </si>
-  <si>
-    <t>4607840199d0961418033b806c091fa5</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1NtlFDMD0zO9DEv0zSfnDvEan__Jq_KsV</t>
-  </si>
-  <si>
-    <t>QLoRA fine-tuning of Qwen3 on automatically-perturbed claim-evidence pairs derived from SIBiLS/PMC OA tables and figures</t>
-  </si>
-  <si>
-    <t>6607f586a28e28900dc37020cf21d625</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1xP-Ybn31kaGQDS9Dts8ve2vsuRnFp_XS</t>
-  </si>
-  <si>
-    <t>Qwen3-VL decider + chart/table advisor</t>
-  </si>
-  <si>
-    <t>ChartGemma and PaddleOCR act as advisors, extracting figure interpretations and table structure respectively, which Qwen uses to make the final decision</t>
-  </si>
-  <si>
-    <t>ddcfd68c99ae727089638c31c1da07e2</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1y049nj1HHxdpPPPWaDQAnBs8WVJKGciL</t>
-  </si>
-  <si>
-    <t>subtask1-one-stage-thinking</t>
-  </si>
-  <si>
-    <t>cdbdf8cdaec530a81de30d0fa3927443</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1_ygoFIGlit7gBAQYmghQt3M7IoMxu8vh</t>
-  </si>
-  <si>
-    <t>v8</t>
-  </si>
-  <si>
     <t>f2ee96c1d439b3caa08851e42d5b7000</t>
   </si>
   <si>
@@ -1726,309 +1756,6 @@
   </si>
   <si>
     <t>baseline_phi4_14B_qwen_vl</t>
-  </si>
-  <si>
-    <t>eaba2ac274b0c606725e764419e82552</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1AckeyWWuawlutcZ0fWoiBgoztRfK-h4Z</t>
-  </si>
-  <si>
-    <t>CommitID: bf1bce5</t>
-  </si>
-  <si>
-    <t>69130f5806bb87851690bd623f6d70d8</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1i3tMkTIF_QTWJq3VG0yoGGORFqMTNcMH</t>
-  </si>
-  <si>
-    <t>v9</t>
-  </si>
-  <si>
-    <t>249d7a0e5ad4877a57d3aefcb669a930</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=17LmdOBudHSa6GO3wheBfrjr8XHlpkRxD</t>
-  </si>
-  <si>
-    <t>2e2e8b28fa20c0070ca9d592d494e5b4</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1nlgWtXlR1uLHnp7qICMq7iahRBulMMqh</t>
-  </si>
-  <si>
-    <t>daf1d60cb0b82a5747733a605efc11f1</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1-8WT9MlOcG62Da6L9_Yn2PduZ41N10Yd</t>
-  </si>
-  <si>
-    <t>fixed</t>
-  </si>
-  <si>
-    <t>c8a371d1baa6f2934ea62d457c24dc79</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1av4H2wf4z-oDnmR3wUAgFXGBW3nT1mTM</t>
-  </si>
-  <si>
-    <t>image input + CoT + pairwise inference + gemma4 31b none thinking</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Group ID</t>
-  </si>
-  <si>
-    <t>Group Name</t>
-  </si>
-  <si>
-    <t>PI Email</t>
-  </si>
-  <si>
-    <t>CP Email</t>
-  </si>
-  <si>
-    <t>Member1 Email</t>
-  </si>
-  <si>
-    <t>Member2 Email</t>
-  </si>
-  <si>
-    <t>Member3 Email</t>
-  </si>
-  <si>
-    <t>Member4 Email</t>
-  </si>
-  <si>
-    <t>luc.mottin@hesge.ch</t>
-  </si>
-  <si>
-    <t>alexandre.flament@hesge.ch</t>
-  </si>
-  <si>
-    <t>julien.knafou@hes-so.ch</t>
-  </si>
-  <si>
-    <t>anais.mottaz@hesge.ch</t>
-  </si>
-  <si>
-    <t>patrick.ruch@hesge.ch</t>
-  </si>
-  <si>
-    <t>srawat@uni-bonn.de</t>
-  </si>
-  <si>
-    <t>hu.zhao@fz-juelich.de</t>
-  </si>
-  <si>
-    <t>we.yu@fz-juelich.de</t>
-  </si>
-  <si>
-    <t>JNLP</t>
-  </si>
-  <si>
-    <t>nguyenml@jaist.ac.jp</t>
-  </si>
-  <si>
-    <t>trungvo@jaist.ac.jp</t>
-  </si>
-  <si>
-    <t>ntdminh@jaist.ac.jp</t>
-  </si>
-  <si>
-    <t>xiuzhen.zhang@rmit.edu.au</t>
-  </si>
-  <si>
-    <t>s3888611@student.rmit.edu.au</t>
-  </si>
-  <si>
-    <t>UQAI</t>
-  </si>
-  <si>
-    <t>The University of Queensland AI Lab</t>
-  </si>
-  <si>
-    <t>s.culpepper@uq.edu.au</t>
-  </si>
-  <si>
-    <t>s4984662@student.uq.edu.au</t>
-  </si>
-  <si>
-    <t>Penn18</t>
-  </si>
-  <si>
-    <t>University of Pennsylvania SciFy team</t>
-  </si>
-  <si>
-    <t>ccb@seas.upenn.edu</t>
-  </si>
-  <si>
-    <t>delip@seas.upenn.edu</t>
-  </si>
-  <si>
-    <t>muxinliu@seas.upenn.edu</t>
-  </si>
-  <si>
-    <t>WITM</t>
-  </si>
-  <si>
-    <t>TCS Research NTCIR Team</t>
-  </si>
-  <si>
-    <t>diya.saha@tcs.com</t>
-  </si>
-  <si>
-    <t>sem03@soton.ac.uk</t>
-  </si>
-  <si>
-    <t>Rudra.Mutalik@soton.ac.uk</t>
-  </si>
-  <si>
-    <t>ajs502@soton.ac.uk</t>
-  </si>
-  <si>
-    <t>Denso IT Laboratory NTCIR team</t>
-  </si>
-  <si>
-    <t>tachioka.yuki@core.d-itlab.co.jp</t>
-  </si>
-  <si>
-    <t>tsukahara.hiroshi@core.d-itlab.co.jp</t>
-  </si>
-  <si>
-    <t>terao.yasunori@core.d-itlab.co.jp</t>
-  </si>
-  <si>
-    <t>matthes@tum.de</t>
-  </si>
-  <si>
-    <t>tejaswi.choppa@tum.de</t>
-  </si>
-  <si>
-    <t>TakasuLab</t>
-  </si>
-  <si>
-    <t>kawakatsu@preferred.jp</t>
-  </si>
-  <si>
-    <t>namlytuan@gmail.com</t>
-  </si>
-  <si>
-    <t>Pro²Crast</t>
-  </si>
-  <si>
-    <t>takeda@nii.ac.jp</t>
-  </si>
-  <si>
-    <t>duymn@nii.ac.jp</t>
-  </si>
-  <si>
-    <t>koolsha123@gmail.com</t>
-  </si>
-  <si>
-    <t>natt@jaist.ac.jp</t>
-  </si>
-  <si>
-    <t>anak_ponggun@cmu.ac.th</t>
-  </si>
-  <si>
-    <t>w.patipon@jaist.ac.jp</t>
-  </si>
-  <si>
-    <t>areerat.t@cmu.ac.th</t>
-  </si>
-  <si>
-    <t>nejdl@l3s.de</t>
-  </si>
-  <si>
-    <t>schrader@l3s.de</t>
-  </si>
-  <si>
-    <t>xiang.zhou@stud.uni-hannover.de</t>
-  </si>
-  <si>
-    <t>Bichtemann.Sven@mh-hannover.de</t>
-  </si>
-  <si>
-    <t>YUNTrust</t>
-  </si>
-  <si>
-    <t>TrustIS Lab</t>
-  </si>
-  <si>
-    <t>dongyy929@ynu.edu.cn</t>
-  </si>
-  <si>
-    <t>2151242847@qq.com</t>
-  </si>
-  <si>
-    <t>lifanxiao15@outlook.com</t>
-  </si>
-  <si>
-    <t>tonkotsu</t>
-  </si>
-  <si>
-    <t>ScAIHub</t>
-  </si>
-  <si>
-    <t>dren.fazlija@l3s.de</t>
-  </si>
-  <si>
-    <t>avellino@stud.uni-hannover.de</t>
-  </si>
-  <si>
-    <t>renataarcos1@hotmail.com</t>
-  </si>
-  <si>
-    <t>rathee@l3s.de</t>
-  </si>
-  <si>
-    <t>mike.gill@stud.uni-hannover.de</t>
-  </si>
-  <si>
-    <t>khyzar.baig@stud.uni-hannover.de</t>
-  </si>
-  <si>
-    <t>vimal.subbiah@stud.uni-hannover.de</t>
-  </si>
-  <si>
-    <t>NYUVA</t>
-  </si>
-  <si>
-    <t>NYU - Vasudev Awatramani</t>
-  </si>
-  <si>
-    <t>va2134@nyu.edu</t>
-  </si>
-  <si>
-    <t>alexander.fraser@tum.de</t>
-  </si>
-  <si>
-    <t>anna.steinberg@lmu.de</t>
-  </si>
-  <si>
-    <t>UBCS</t>
-  </si>
-  <si>
-    <t>University of Botswana Computer Science Team</t>
-  </si>
-  <si>
-    <t>andersong@ub.ac.bw</t>
-  </si>
-  <si>
-    <t>thumae@ub.ac.bw</t>
-  </si>
-  <si>
-    <t>qiming.bao@auckland.ac.nz</t>
-  </si>
-  <si>
-    <t>neset.tan@auckland.ac.nz</t>
-  </si>
-  <si>
-    <t>Number of Submissions</t>
   </si>
   <si>
     <t>pair_accuracy</t>
@@ -2041,7 +1768,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2060,35 +1787,16 @@
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2096,41 +1804,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2169,42 +1847,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="4">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -2230,29 +1892,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Run Evaluations-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2503,7 +2149,7 @@
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.140625" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="24.42578125" customWidth="1"/>
@@ -2556,7 +2202,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>663</v>
+        <v>577</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>12</v>
@@ -13129,49 +12775,49 @@
         <v>532</v>
       </c>
       <c r="B163" s="8">
-        <v>46223.684386574074</v>
+        <v>46223.759594907409</v>
       </c>
       <c r="C163" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F163" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="D163" s="9" t="s">
+      <c r="G163" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H163" s="7" t="s">
         <v>534</v>
-      </c>
-      <c r="E163" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="G163" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H163" s="7" t="s">
-        <v>536</v>
       </c>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
-      <c r="L163" s="3"/>
+      <c r="L163" s="3">
+        <v>80.28</v>
+      </c>
       <c r="M163" s="3"/>
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
       <c r="P163" s="4"/>
       <c r="Q163" s="4"/>
       <c r="R163" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S163" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T163" s="9"/>
+      <c r="T163" s="9" t="s">
+        <v>535</v>
+      </c>
       <c r="U163" s="11"/>
-      <c r="V163" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="W163" s="9" t="s">
-        <v>537</v>
-      </c>
+      <c r="V163" s="9"/>
+      <c r="W163" s="9"/>
       <c r="X163" s="6"/>
       <c r="Y163" s="6"/>
       <c r="Z163" s="6"/>
@@ -13184,34 +12830,34 @@
     </row>
     <row r="164" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B164" s="8">
-        <v>46223.759594907409</v>
+        <v>46223.765011574076</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>392</v>
+        <v>243</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>393</v>
+        <v>243</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G164" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H164" s="7" t="s">
-        <v>540</v>
+        <v>280</v>
       </c>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="3">
-        <v>80.28</v>
+        <v>79.819999999999993</v>
       </c>
       <c r="M164" s="3"/>
       <c r="N164" s="4"/>
@@ -13224,9 +12870,7 @@
       <c r="S164" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T164" s="9" t="s">
-        <v>541</v>
-      </c>
+      <c r="T164" s="9"/>
       <c r="U164" s="11"/>
       <c r="V164" s="9"/>
       <c r="W164" s="9"/>
@@ -13242,47 +12886,65 @@
     </row>
     <row r="165" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B165" s="8">
-        <v>46223.765011574076</v>
+        <v>46223.779502314814</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>243</v>
+        <v>505</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I165" s="3"/>
-      <c r="J165" s="3"/>
-      <c r="K165" s="3"/>
+        <v>507</v>
+      </c>
+      <c r="I165" s="3">
+        <v>84.31</v>
+      </c>
+      <c r="J165" s="3">
+        <v>84.41</v>
+      </c>
+      <c r="K165" s="3">
+        <v>84.35</v>
+      </c>
       <c r="L165" s="3">
-        <v>79.819999999999993</v>
-      </c>
-      <c r="M165" s="3"/>
-      <c r="N165" s="4"/>
-      <c r="O165" s="4"/>
-      <c r="P165" s="4"/>
-      <c r="Q165" s="4"/>
+        <v>84.41</v>
+      </c>
+      <c r="M165" s="3">
+        <v>70.87</v>
+      </c>
+      <c r="N165" s="4">
+        <v>359</v>
+      </c>
+      <c r="O165" s="4">
+        <v>77</v>
+      </c>
+      <c r="P165" s="4">
+        <v>66</v>
+      </c>
+      <c r="Q165" s="4">
+        <v>415</v>
+      </c>
       <c r="R165" s="9" t="s">
         <v>29</v>
       </c>
       <c r="S165" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T165" s="9"/>
+      <c r="T165" s="9" t="s">
+        <v>508</v>
+      </c>
       <c r="U165" s="11"/>
       <c r="V165" s="9"/>
       <c r="W165" s="9"/>
@@ -13298,55 +12960,55 @@
     </row>
     <row r="166" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B166" s="8">
-        <v>46223.779502314814</v>
+        <v>46223.780636574076</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>504</v>
+        <v>392</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>505</v>
+        <v>393</v>
       </c>
       <c r="E166" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="H166" s="7" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="I166" s="3">
-        <v>84.31</v>
+        <v>79.61</v>
       </c>
       <c r="J166" s="3">
-        <v>84.41</v>
+        <v>79.66</v>
       </c>
       <c r="K166" s="3">
-        <v>84.35</v>
+        <v>79.39</v>
       </c>
       <c r="L166" s="3">
-        <v>84.41</v>
+        <v>79.39</v>
       </c>
       <c r="M166" s="3">
-        <v>70.87</v>
+        <v>61.7</v>
       </c>
       <c r="N166" s="4">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O166" s="4">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P166" s="4">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="Q166" s="4">
-        <v>415</v>
+        <v>361</v>
       </c>
       <c r="R166" s="9" t="s">
         <v>29</v>
@@ -13355,7 +13017,7 @@
         <v>29</v>
       </c>
       <c r="T166" s="9" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="U166" s="11"/>
       <c r="V166" s="9"/>
@@ -13372,10 +13034,10 @@
     </row>
     <row r="167" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B167" s="8">
-        <v>46223.780636574076</v>
+        <v>46223.790439814817</v>
       </c>
       <c r="C167" s="9" t="s">
         <v>392</v>
@@ -13384,44 +13046,28 @@
         <v>393</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H167" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="I167" s="3">
-        <v>79.61</v>
-      </c>
-      <c r="J167" s="3">
-        <v>79.66</v>
-      </c>
-      <c r="K167" s="3">
-        <v>79.39</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="I167" s="3"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
       <c r="L167" s="3">
-        <v>79.39</v>
-      </c>
-      <c r="M167" s="3">
-        <v>61.7</v>
-      </c>
-      <c r="N167" s="4">
-        <v>367</v>
-      </c>
-      <c r="O167" s="4">
-        <v>69</v>
-      </c>
-      <c r="P167" s="4">
-        <v>120</v>
-      </c>
-      <c r="Q167" s="4">
-        <v>361</v>
-      </c>
+        <v>79.819999999999993</v>
+      </c>
+      <c r="M167" s="3"/>
+      <c r="N167" s="4"/>
+      <c r="O167" s="4"/>
+      <c r="P167" s="4"/>
+      <c r="Q167" s="4"/>
       <c r="R167" s="9" t="s">
         <v>29</v>
       </c>
@@ -13429,7 +13075,7 @@
         <v>29</v>
       </c>
       <c r="T167" s="9" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="U167" s="11"/>
       <c r="V167" s="9"/>
@@ -13446,49 +13092,63 @@
     </row>
     <row r="168" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B168" s="8">
+        <v>46223.826111111113</v>
+      </c>
+      <c r="C168" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F168" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H168" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="B168" s="8">
-        <v>46223.790439814817</v>
-      </c>
-      <c r="C168" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="D168" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E168" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F168" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="G168" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H168" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="I168" s="3"/>
-      <c r="J168" s="3"/>
-      <c r="K168" s="3"/>
+      <c r="I168" s="3">
+        <v>72.709999999999994</v>
+      </c>
+      <c r="J168" s="3">
+        <v>72.680000000000007</v>
+      </c>
+      <c r="K168" s="3">
+        <v>72.69</v>
+      </c>
       <c r="L168" s="3">
-        <v>79.819999999999993</v>
-      </c>
-      <c r="M168" s="3"/>
-      <c r="N168" s="4"/>
-      <c r="O168" s="4"/>
-      <c r="P168" s="4"/>
-      <c r="Q168" s="4"/>
+        <v>72.739999999999995</v>
+      </c>
+      <c r="M168" s="3">
+        <v>52.75</v>
+      </c>
+      <c r="N168" s="4">
+        <v>315</v>
+      </c>
+      <c r="O168" s="4">
+        <v>121</v>
+      </c>
+      <c r="P168" s="4">
+        <v>129</v>
+      </c>
+      <c r="Q168" s="4">
+        <v>352</v>
+      </c>
       <c r="R168" s="9" t="s">
         <v>29</v>
       </c>
       <c r="S168" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T168" s="9" t="s">
-        <v>552</v>
-      </c>
+      <c r="T168" s="9"/>
       <c r="U168" s="11"/>
       <c r="V168" s="9"/>
       <c r="W168" s="9"/>
@@ -13504,56 +13164,40 @@
     </row>
     <row r="169" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B169" s="8">
-        <v>46223.826111111113</v>
+        <v>46223.843530092592</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>351</v>
+        <v>243</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>351</v>
+        <v>243</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="H169" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="I169" s="3">
-        <v>72.709999999999994</v>
-      </c>
-      <c r="J169" s="3">
-        <v>72.680000000000007</v>
-      </c>
-      <c r="K169" s="3">
-        <v>72.69</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="I169" s="3"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3"/>
       <c r="L169" s="3">
-        <v>72.739999999999995</v>
-      </c>
-      <c r="M169" s="3">
-        <v>52.75</v>
-      </c>
-      <c r="N169" s="4">
-        <v>315</v>
-      </c>
-      <c r="O169" s="4">
-        <v>121</v>
-      </c>
-      <c r="P169" s="4">
-        <v>129</v>
-      </c>
-      <c r="Q169" s="4">
-        <v>352</v>
-      </c>
+        <v>80.05</v>
+      </c>
+      <c r="M169" s="3"/>
+      <c r="N169" s="4"/>
+      <c r="O169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="4"/>
       <c r="R169" s="9" t="s">
         <v>29</v>
       </c>
@@ -13576,47 +13220,65 @@
     </row>
     <row r="170" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B170" s="8">
-        <v>46223.843530092592</v>
+        <v>46223.868206018517</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>243</v>
+        <v>505</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H170" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="I170" s="3"/>
-      <c r="J170" s="3"/>
-      <c r="K170" s="3"/>
+        <v>507</v>
+      </c>
+      <c r="I170" s="3">
+        <v>85.74</v>
+      </c>
+      <c r="J170" s="3">
+        <v>86.11</v>
+      </c>
+      <c r="K170" s="3">
+        <v>85.84</v>
+      </c>
       <c r="L170" s="3">
-        <v>80.05</v>
-      </c>
-      <c r="M170" s="3"/>
-      <c r="N170" s="4"/>
-      <c r="O170" s="4"/>
-      <c r="P170" s="4"/>
-      <c r="Q170" s="4"/>
+        <v>85.93</v>
+      </c>
+      <c r="M170" s="3">
+        <v>73.17</v>
+      </c>
+      <c r="N170" s="4">
+        <v>357</v>
+      </c>
+      <c r="O170" s="4">
+        <v>79</v>
+      </c>
+      <c r="P170" s="4">
+        <v>50</v>
+      </c>
+      <c r="Q170" s="4">
+        <v>431</v>
+      </c>
       <c r="R170" s="9" t="s">
         <v>29</v>
       </c>
       <c r="S170" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T170" s="9"/>
+      <c r="T170" s="9" t="s">
+        <v>555</v>
+      </c>
       <c r="U170" s="11"/>
       <c r="V170" s="9"/>
       <c r="W170" s="9"/>
@@ -13632,52 +13294,50 @@
     </row>
     <row r="171" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B171" s="8">
-        <v>46223.854432870372</v>
+        <v>46223.872037037036</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>533</v>
+        <v>243</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>534</v>
+        <v>243</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
-      <c r="L171" s="3"/>
+      <c r="L171" s="3">
+        <v>50</v>
+      </c>
       <c r="M171" s="3"/>
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
       <c r="P171" s="4"/>
       <c r="Q171" s="4"/>
       <c r="R171" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S171" s="9" t="s">
         <v>29</v>
       </c>
       <c r="T171" s="9"/>
       <c r="U171" s="11"/>
-      <c r="V171" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="W171" s="9" t="s">
-        <v>537</v>
-      </c>
+      <c r="V171" s="9"/>
+      <c r="W171" s="9"/>
       <c r="X171" s="6"/>
       <c r="Y171" s="6"/>
       <c r="Z171" s="6"/>
@@ -13690,10 +13350,10 @@
     </row>
     <row r="172" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B172" s="8">
-        <v>46223.868206018517</v>
+        <v>46223.873240740744</v>
       </c>
       <c r="C172" s="9" t="s">
         <v>504</v>
@@ -13702,10 +13362,10 @@
         <v>505</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="G172" s="7" t="s">
         <v>26</v>
@@ -13713,33 +13373,17 @@
       <c r="H172" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="I172" s="3">
-        <v>85.74</v>
-      </c>
-      <c r="J172" s="3">
-        <v>86.11</v>
-      </c>
-      <c r="K172" s="3">
-        <v>85.84</v>
-      </c>
+      <c r="I172" s="3"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
       <c r="L172" s="3">
-        <v>85.93</v>
-      </c>
-      <c r="M172" s="3">
-        <v>73.17</v>
-      </c>
-      <c r="N172" s="4">
-        <v>357</v>
-      </c>
-      <c r="O172" s="4">
-        <v>79</v>
-      </c>
-      <c r="P172" s="4">
-        <v>50</v>
-      </c>
-      <c r="Q172" s="4">
-        <v>431</v>
-      </c>
+        <v>93.58</v>
+      </c>
+      <c r="M172" s="3"/>
+      <c r="N172" s="4"/>
+      <c r="O172" s="4"/>
+      <c r="P172" s="4"/>
+      <c r="Q172" s="4"/>
       <c r="R172" s="9" t="s">
         <v>29</v>
       </c>
@@ -13747,7 +13391,7 @@
         <v>29</v>
       </c>
       <c r="T172" s="9" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="U172" s="11"/>
       <c r="V172" s="9"/>
@@ -13764,34 +13408,34 @@
     </row>
     <row r="173" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B173" s="8">
-        <v>46223.872037037036</v>
+        <v>46223.874432870369</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>243</v>
+        <v>504</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>243</v>
+        <v>505</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G173" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="3">
-        <v>50</v>
+        <v>93.58</v>
       </c>
       <c r="M173" s="3"/>
       <c r="N173" s="4"/>
@@ -13804,7 +13448,9 @@
       <c r="S173" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T173" s="9"/>
+      <c r="T173" s="9" t="s">
+        <v>555</v>
+      </c>
       <c r="U173" s="11"/>
       <c r="V173" s="9"/>
       <c r="W173" s="9"/>
@@ -13820,34 +13466,34 @@
     </row>
     <row r="174" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B174" s="8">
-        <v>46223.873240740744</v>
+        <v>46224.043553240743</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>504</v>
+        <v>243</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>505</v>
+        <v>243</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G174" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H174" s="7" t="s">
-        <v>507</v>
+        <v>558</v>
       </c>
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="3">
-        <v>93.58</v>
+        <v>75.92</v>
       </c>
       <c r="M174" s="3"/>
       <c r="N174" s="4"/>
@@ -13861,7 +13507,7 @@
         <v>29</v>
       </c>
       <c r="T174" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="U174" s="11"/>
       <c r="V174" s="9"/>
@@ -13878,49 +13524,63 @@
     </row>
     <row r="175" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B175" s="8">
-        <v>46223.874432870369</v>
+        <v>46224.563645833332</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>504</v>
+        <v>114</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>505</v>
+        <v>115</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="I175" s="3"/>
-      <c r="J175" s="3"/>
-      <c r="K175" s="3"/>
+        <v>568</v>
+      </c>
+      <c r="I175" s="3">
+        <v>92.62</v>
+      </c>
+      <c r="J175" s="3">
+        <v>92.55</v>
+      </c>
+      <c r="K175" s="3">
+        <v>92.57</v>
+      </c>
       <c r="L175" s="3">
-        <v>93.58</v>
-      </c>
-      <c r="M175" s="3"/>
-      <c r="N175" s="4"/>
-      <c r="O175" s="4"/>
-      <c r="P175" s="4"/>
-      <c r="Q175" s="4"/>
+        <v>92.58</v>
+      </c>
+      <c r="M175" s="3">
+        <v>87.84</v>
+      </c>
+      <c r="N175" s="4">
+        <v>407</v>
+      </c>
+      <c r="O175" s="4">
+        <v>29</v>
+      </c>
+      <c r="P175" s="4">
+        <v>39</v>
+      </c>
+      <c r="Q175" s="4">
+        <v>442</v>
+      </c>
       <c r="R175" s="9" t="s">
         <v>29</v>
       </c>
       <c r="S175" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T175" s="9" t="s">
-        <v>564</v>
-      </c>
+      <c r="T175" s="9"/>
       <c r="U175" s="11"/>
       <c r="V175" s="9"/>
       <c r="W175" s="9"/>
@@ -13936,49 +13596,63 @@
     </row>
     <row r="176" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46223.684386574074</v>
+      </c>
+      <c r="C176" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F176" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="B176" s="8">
-        <v>46224.043553240743</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="E176" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F176" s="10" t="s">
+      <c r="G176" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H176" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="G176" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H176" s="7" t="s">
-        <v>567</v>
-      </c>
-      <c r="I176" s="3"/>
-      <c r="J176" s="3"/>
-      <c r="K176" s="3"/>
+      <c r="I176" s="3">
+        <v>64.83</v>
+      </c>
+      <c r="J176" s="3">
+        <v>65.87</v>
+      </c>
+      <c r="K176" s="3">
+        <v>64.58</v>
+      </c>
       <c r="L176" s="3">
-        <v>75.92</v>
-      </c>
-      <c r="M176" s="3"/>
-      <c r="N176" s="4"/>
-      <c r="O176" s="4"/>
-      <c r="P176" s="4"/>
-      <c r="Q176" s="4"/>
+        <v>65.430000000000007</v>
+      </c>
+      <c r="M176" s="3">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="N176" s="4">
+        <v>229</v>
+      </c>
+      <c r="O176" s="4">
+        <v>207</v>
+      </c>
+      <c r="P176" s="4">
+        <v>110</v>
+      </c>
+      <c r="Q176" s="4">
+        <v>371</v>
+      </c>
       <c r="R176" s="9" t="s">
         <v>29</v>
       </c>
       <c r="S176" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="T176" s="9" t="s">
-        <v>574</v>
-      </c>
+      <c r="T176" s="9"/>
       <c r="U176" s="11"/>
       <c r="V176" s="9"/>
       <c r="W176" s="9"/>
@@ -13994,55 +13668,55 @@
     </row>
     <row r="177" spans="1:32" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B177" s="8">
-        <v>46224.563645833332</v>
+        <v>46223.854432870372</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>114</v>
+        <v>570</v>
       </c>
       <c r="D177" s="9" t="s">
-        <v>115</v>
+        <v>571</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>117</v>
       </c>
       <c r="H177" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="I177" s="3">
-        <v>92.62</v>
+        <v>64.83</v>
       </c>
       <c r="J177" s="3">
-        <v>92.55</v>
+        <v>65.87</v>
       </c>
       <c r="K177" s="3">
-        <v>92.57</v>
+        <v>64.58</v>
       </c>
       <c r="L177" s="3">
-        <v>92.58</v>
+        <v>65.430000000000007</v>
       </c>
       <c r="M177" s="3">
-        <v>87.84</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N177" s="4">
-        <v>407</v>
+        <v>229</v>
       </c>
       <c r="O177" s="4">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="P177" s="4">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="Q177" s="4">
-        <v>442</v>
+        <v>371</v>
       </c>
       <c r="R177" s="9" t="s">
         <v>29</v>
@@ -48520,640 +48194,4 @@
     <tablePart r:id="rId177"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0106C7A7-0150-434B-BB64-317C8664B76C}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="21" customWidth="1"/>
-    <col min="5" max="10" width="31.5703125" customWidth="1"/>
-    <col min="12" max="12" width="30.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
-        <v>578</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>580</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>662</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>581</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>585</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="15">
-        <v>17</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="D2" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B2)</f>
-        <v>8</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>587</v>
-      </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="18" t="s">
-        <v>588</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>589</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>590</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="15">
-        <v>30</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B3)</f>
-        <v>44</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>592</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="18" t="s">
-        <v>593</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>594</v>
-      </c>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15">
-        <v>40</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>595</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>595</v>
-      </c>
-      <c r="D4" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B4)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>598</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-    </row>
-    <row r="5" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="15">
-        <v>52</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B5)</f>
-        <v>10</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>599</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>600</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="15">
-        <v>56</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="D6" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B6)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="15">
-        <v>59</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>605</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>606</v>
-      </c>
-      <c r="D7" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B7)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>607</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="15">
-        <v>16</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="D8" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B8)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>612</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15">
-        <v>64</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B9)</f>
-        <v>2</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>615</v>
-      </c>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="15">
-        <v>73</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="D10" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B10)</f>
-        <v>5</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>619</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="15">
-        <v>77</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B11)</f>
-        <v>2</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>620</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>621</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="15">
-        <v>81</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>504</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="D12" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B12)</f>
-        <v>7</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="18" t="s">
-        <v>624</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="15">
-        <v>85</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="D13" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B13)</f>
-        <v>27</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15">
-        <v>95</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="D14" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B14)</f>
-        <v>4</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="J14" s="19"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="15">
-        <v>96</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B15)</f>
-        <v>30</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>634</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>635</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>636</v>
-      </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="15">
-        <v>99</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>637</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>638</v>
-      </c>
-      <c r="D16" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B16)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>639</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>640</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>641</v>
-      </c>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="15">
-        <v>100</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>643</v>
-      </c>
-      <c r="D17" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>644</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="18" t="s">
-        <v>645</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>646</v>
-      </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="15">
-        <v>101</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="D18" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B18)</f>
-        <v>4</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>647</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>648</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>649</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>650</v>
-      </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="15">
-        <v>102</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>651</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>652</v>
-      </c>
-      <c r="D19" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B19)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>653</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="15">
-        <v>106</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="D20" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B20)</f>
-        <v>7</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>654</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>655</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="15">
-        <v>117</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>656</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>657</v>
-      </c>
-      <c r="D21" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B21)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>658</v>
-      </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18" t="s">
-        <v>659</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="15">
-        <v>118</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="21">
-        <f>COUNTIF('Run Evaluations'!$C:$C,$B22)</f>
-        <v>8</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>660</v>
-      </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="18" t="s">
-        <v>661</v>
-      </c>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{61859998-8DDE-48D9-B77C-96B5094BEF54}">
-            <xm:f>COUNTIF('Run Evaluations'!$C:$C,$B2)&gt;0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="2" id="{805CD774-A340-40C0-82DD-E660FD32B932}">
-            <xm:f>COUNTIF('Run Evaluations'!$C:$C,$B2)=0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B2:B22</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
 </file>
--- a/assets/SciClaimEval26_Results.xlsx
+++ b/assets/SciClaimEval26_Results.xlsx
@@ -5,13 +5,15 @@
   <sheets>
     <sheet state="visible" name="Run Evaluations" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Run Evaluations'!$A$1:$W$195</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="625">
   <si>
     <t>run_id</t>
   </si>
@@ -1832,6 +1834,66 @@
   </si>
   <si>
     <t>task1_routed_gptfable_SUBMIT</t>
+  </si>
+  <si>
+    <t>107fcb2da277a9ef2c526b8e265519ac</t>
+  </si>
+  <si>
+    <t>c0fb6fb246183c26400846a6656f2e0e</t>
+  </si>
+  <si>
+    <t>c1827e6c87b9a63f1d4e94ab9e9d70ea</t>
+  </si>
+  <si>
+    <t>fca8b45e3cc41568c3431721504e1bae</t>
+  </si>
+  <si>
+    <t>51744d10e0fca05a8dc564292920d5ab</t>
+  </si>
+  <si>
+    <t>4753ecef98b994f160bd27bccba435c4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IgkG9k5jrd4bNPie9IXTerex-UnRnliD</t>
+  </si>
+  <si>
+    <t>Claude Fable 5 (PNG-only)</t>
+  </si>
+  <si>
+    <t>b5684ef7e9b3f054fcf66f8cc4f04577</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1abF4tMdtqA4Y5szJYrHoAWo8U7JkTW9l</t>
+  </si>
+  <si>
+    <t>routed ensemble + GPT-5.5 + pair prior (PNG-only, leak-free)</t>
+  </si>
+  <si>
+    <t>a184f4b6fde90fa4d3e80cabf5fa83d8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1LnDVc7K5xQ81xuMwB6QrkhZUc5lIxqQQ</t>
+  </si>
+  <si>
+    <t>routed ensemble + GPT-5.5 + Claude Fable 5 + pair prior (PNG-only, leak-free)</t>
+  </si>
+  <si>
+    <t>fd0f6d66d0d1d3cd9fe4daa782bee6c9</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=19VIoDpOhxPBzmxLfcglZqTqvRfOUdVSn</t>
+  </si>
+  <si>
+    <t>GPT 5.6 Sol</t>
+  </si>
+  <si>
+    <t>8104ad3204c680583aca8f143f0f9678</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=16AE02HDl_qEQihsAS-KSibJ4gOpwFR5p</t>
+  </si>
+  <si>
+    <t>routed ensemble + GPT-5.5 + Claude Fable 5 + GPT-5.6 Sol + pair prior (PNG-only, leak-free)</t>
   </si>
 </sst>
 </file>
@@ -1995,7 +2057,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:W185" displayName="SciClaimEval26_Results" name="SciClaimEval26_Results" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:W195" displayName="SciClaimEval26_Results" name="SciClaimEval26_Results" id="1">
+  <autoFilter ref="$A$1:$W$195"/>
   <tableColumns count="23">
     <tableColumn name="run_id" id="1"/>
     <tableColumn name="timestamp" id="2"/>
@@ -14355,30 +14418,68 @@
       <c r="AE185" s="6"/>
       <c r="AF185" s="6"/>
     </row>
-    <row r="186">
-      <c r="A186" s="12"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="12"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="12"/>
-      <c r="I186" s="13"/>
-      <c r="J186" s="13"/>
-      <c r="K186" s="13"/>
-      <c r="L186" s="13"/>
-      <c r="M186" s="13"/>
-      <c r="N186" s="13"/>
-      <c r="O186" s="13"/>
-      <c r="P186" s="13"/>
-      <c r="Q186" s="13"/>
-      <c r="R186" s="6"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
+    <row r="186" ht="22.5" customHeight="1">
+      <c r="A186" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="B186" s="8">
+        <v>46202.85901620371</v>
+      </c>
+      <c r="C186" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E186" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="I186" s="3">
+        <v>97.37</v>
+      </c>
+      <c r="J186" s="3">
+        <v>97.33</v>
+      </c>
+      <c r="K186" s="3">
+        <v>97.35</v>
+      </c>
+      <c r="L186" s="3">
+        <v>97.35</v>
+      </c>
+      <c r="M186" s="3">
+        <v>97.69</v>
+      </c>
+      <c r="N186" s="4">
+        <v>422.0</v>
+      </c>
+      <c r="O186" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="P186" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>460.0</v>
+      </c>
+      <c r="R186" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S186" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T186" s="11"/>
+      <c r="U186" s="11"/>
+      <c r="V186" s="9"/>
+      <c r="W186" s="9"/>
       <c r="X186" s="6"/>
       <c r="Y186" s="6"/>
       <c r="Z186" s="6"/>
@@ -14389,30 +14490,68 @@
       <c r="AE186" s="6"/>
       <c r="AF186" s="6"/>
     </row>
-    <row r="187">
-      <c r="A187" s="12"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="12"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="12"/>
-      <c r="I187" s="13"/>
-      <c r="J187" s="13"/>
-      <c r="K187" s="13"/>
-      <c r="L187" s="13"/>
-      <c r="M187" s="13"/>
-      <c r="N187" s="13"/>
-      <c r="O187" s="13"/>
-      <c r="P187" s="13"/>
-      <c r="Q187" s="13"/>
-      <c r="R187" s="6"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
+    <row r="187" ht="22.5" customHeight="1">
+      <c r="A187" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B187" s="8">
+        <v>46210.876747685186</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H187" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="I187" s="3">
+        <v>98.13</v>
+      </c>
+      <c r="J187" s="3">
+        <v>98.11</v>
+      </c>
+      <c r="K187" s="3">
+        <v>98.12</v>
+      </c>
+      <c r="L187" s="3">
+        <v>98.12</v>
+      </c>
+      <c r="M187" s="3">
+        <v>98.38</v>
+      </c>
+      <c r="N187" s="4">
+        <v>425.0</v>
+      </c>
+      <c r="O187" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="P187" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="Q187" s="4">
+        <v>464.0</v>
+      </c>
+      <c r="R187" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S187" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T187" s="11"/>
+      <c r="U187" s="11"/>
+      <c r="V187" s="9"/>
+      <c r="W187" s="9"/>
       <c r="X187" s="6"/>
       <c r="Y187" s="6"/>
       <c r="Z187" s="6"/>
@@ -14423,30 +14562,68 @@
       <c r="AE187" s="6"/>
       <c r="AF187" s="6"/>
     </row>
-    <row r="188">
-      <c r="A188" s="12"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="12"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="12"/>
-      <c r="I188" s="13"/>
-      <c r="J188" s="13"/>
-      <c r="K188" s="13"/>
-      <c r="L188" s="13"/>
-      <c r="M188" s="13"/>
-      <c r="N188" s="13"/>
-      <c r="O188" s="13"/>
-      <c r="P188" s="13"/>
-      <c r="Q188" s="13"/>
-      <c r="R188" s="6"/>
-      <c r="S188" s="6"/>
-      <c r="T188" s="6"/>
-      <c r="U188" s="6"/>
-      <c r="V188" s="6"/>
-      <c r="W188" s="6"/>
+    <row r="188" ht="22.5" customHeight="1">
+      <c r="A188" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="B188" s="8">
+        <v>46210.8775</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="G188" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="I188" s="3">
+        <v>96.92</v>
+      </c>
+      <c r="J188" s="3">
+        <v>96.89</v>
+      </c>
+      <c r="K188" s="3">
+        <v>96.9</v>
+      </c>
+      <c r="L188" s="3">
+        <v>96.91</v>
+      </c>
+      <c r="M188" s="3">
+        <v>97.22</v>
+      </c>
+      <c r="N188" s="4">
+        <v>420.0</v>
+      </c>
+      <c r="O188" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="P188" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="Q188" s="4">
+        <v>458.0</v>
+      </c>
+      <c r="R188" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S188" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T188" s="11"/>
+      <c r="U188" s="11"/>
+      <c r="V188" s="9"/>
+      <c r="W188" s="9"/>
       <c r="X188" s="6"/>
       <c r="Y188" s="6"/>
       <c r="Z188" s="6"/>
@@ -14457,30 +14634,68 @@
       <c r="AE188" s="6"/>
       <c r="AF188" s="6"/>
     </row>
-    <row r="189">
-      <c r="A189" s="12"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="12"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="12"/>
-      <c r="I189" s="13"/>
-      <c r="J189" s="13"/>
-      <c r="K189" s="13"/>
-      <c r="L189" s="13"/>
-      <c r="M189" s="13"/>
-      <c r="N189" s="13"/>
-      <c r="O189" s="13"/>
-      <c r="P189" s="13"/>
-      <c r="Q189" s="13"/>
-      <c r="R189" s="6"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="A189" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="B189" s="8">
+        <v>46217.75806712963</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H189" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="I189" s="3">
+        <v>96.02</v>
+      </c>
+      <c r="J189" s="3">
+        <v>96.02</v>
+      </c>
+      <c r="K189" s="3">
+        <v>96.02</v>
+      </c>
+      <c r="L189" s="3">
+        <v>96.03</v>
+      </c>
+      <c r="M189" s="3">
+        <v>95.6</v>
+      </c>
+      <c r="N189" s="4">
+        <v>414.0</v>
+      </c>
+      <c r="O189" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="P189" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="Q189" s="4">
+        <v>456.0</v>
+      </c>
+      <c r="R189" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S189" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T189" s="11"/>
+      <c r="U189" s="11"/>
+      <c r="V189" s="9"/>
+      <c r="W189" s="9"/>
       <c r="X189" s="6"/>
       <c r="Y189" s="6"/>
       <c r="Z189" s="6"/>
@@ -14491,30 +14706,68 @@
       <c r="AE189" s="6"/>
       <c r="AF189" s="6"/>
     </row>
-    <row r="190">
-      <c r="A190" s="12"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="12"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="12"/>
-      <c r="I190" s="13"/>
-      <c r="J190" s="13"/>
-      <c r="K190" s="13"/>
-      <c r="L190" s="13"/>
-      <c r="M190" s="13"/>
-      <c r="N190" s="13"/>
-      <c r="O190" s="13"/>
-      <c r="P190" s="13"/>
-      <c r="Q190" s="13"/>
-      <c r="R190" s="6"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="A190" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B190" s="8">
+        <v>46217.76155092593</v>
+      </c>
+      <c r="C190" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="I190" s="3">
+        <v>96.01</v>
+      </c>
+      <c r="J190" s="3">
+        <v>96.03</v>
+      </c>
+      <c r="K190" s="3">
+        <v>96.02</v>
+      </c>
+      <c r="L190" s="3">
+        <v>96.03</v>
+      </c>
+      <c r="M190" s="3">
+        <v>95.37</v>
+      </c>
+      <c r="N190" s="4">
+        <v>413.0</v>
+      </c>
+      <c r="O190" s="4">
+        <v>19.0</v>
+      </c>
+      <c r="P190" s="4">
+        <v>17.0</v>
+      </c>
+      <c r="Q190" s="4">
+        <v>457.0</v>
+      </c>
+      <c r="R190" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S190" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T190" s="11"/>
+      <c r="U190" s="11"/>
+      <c r="V190" s="9"/>
+      <c r="W190" s="9"/>
       <c r="X190" s="6"/>
       <c r="Y190" s="6"/>
       <c r="Z190" s="6"/>
@@ -14525,30 +14778,68 @@
       <c r="AE190" s="6"/>
       <c r="AF190" s="6"/>
     </row>
-    <row r="191">
-      <c r="A191" s="12"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="12"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="12"/>
-      <c r="I191" s="13"/>
-      <c r="J191" s="13"/>
-      <c r="K191" s="13"/>
-      <c r="L191" s="13"/>
-      <c r="M191" s="13"/>
-      <c r="N191" s="13"/>
-      <c r="O191" s="13"/>
-      <c r="P191" s="13"/>
-      <c r="Q191" s="13"/>
-      <c r="R191" s="6"/>
-      <c r="S191" s="6"/>
-      <c r="T191" s="6"/>
-      <c r="U191" s="6"/>
-      <c r="V191" s="6"/>
-      <c r="W191" s="6"/>
+    <row r="191" ht="22.5" customHeight="1">
+      <c r="A191" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B191" s="8">
+        <v>46236.8549537037</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="I191" s="3">
+        <v>98.02</v>
+      </c>
+      <c r="J191" s="3">
+        <v>98.0</v>
+      </c>
+      <c r="K191" s="3">
+        <v>98.01</v>
+      </c>
+      <c r="L191" s="3">
+        <v>98.01</v>
+      </c>
+      <c r="M191" s="3">
+        <v>98.15</v>
+      </c>
+      <c r="N191" s="4">
+        <v>424.0</v>
+      </c>
+      <c r="O191" s="4">
+        <v>8.0</v>
+      </c>
+      <c r="P191" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="Q191" s="4">
+        <v>464.0</v>
+      </c>
+      <c r="R191" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S191" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T191" s="11"/>
+      <c r="U191" s="11"/>
+      <c r="V191" s="9"/>
+      <c r="W191" s="9"/>
       <c r="X191" s="6"/>
       <c r="Y191" s="6"/>
       <c r="Z191" s="6"/>
@@ -14559,30 +14850,68 @@
       <c r="AE191" s="6"/>
       <c r="AF191" s="6"/>
     </row>
-    <row r="192">
-      <c r="A192" s="12"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="12"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="12"/>
-      <c r="I192" s="13"/>
-      <c r="J192" s="13"/>
-      <c r="K192" s="13"/>
-      <c r="L192" s="13"/>
-      <c r="M192" s="13"/>
-      <c r="N192" s="13"/>
-      <c r="O192" s="13"/>
-      <c r="P192" s="13"/>
-      <c r="Q192" s="13"/>
-      <c r="R192" s="6"/>
-      <c r="S192" s="6"/>
-      <c r="T192" s="6"/>
-      <c r="U192" s="6"/>
-      <c r="V192" s="6"/>
-      <c r="W192" s="6"/>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="A192" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B192" s="8">
+        <v>46236.85621527778</v>
+      </c>
+      <c r="C192" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E192" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="I192" s="3">
+        <v>97.25</v>
+      </c>
+      <c r="J192" s="3">
+        <v>97.22</v>
+      </c>
+      <c r="K192" s="3">
+        <v>97.24</v>
+      </c>
+      <c r="L192" s="3">
+        <v>97.24</v>
+      </c>
+      <c r="M192" s="3">
+        <v>97.45</v>
+      </c>
+      <c r="N192" s="4">
+        <v>421.0</v>
+      </c>
+      <c r="O192" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="P192" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="Q192" s="4">
+        <v>460.0</v>
+      </c>
+      <c r="R192" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S192" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T192" s="11"/>
+      <c r="U192" s="11"/>
+      <c r="V192" s="9"/>
+      <c r="W192" s="9"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6"/>
       <c r="Z192" s="6"/>
@@ -14593,30 +14922,68 @@
       <c r="AE192" s="6"/>
       <c r="AF192" s="6"/>
     </row>
-    <row r="193">
-      <c r="A193" s="12"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="12"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="12"/>
-      <c r="I193" s="13"/>
-      <c r="J193" s="13"/>
-      <c r="K193" s="13"/>
-      <c r="L193" s="13"/>
-      <c r="M193" s="13"/>
-      <c r="N193" s="13"/>
-      <c r="O193" s="13"/>
-      <c r="P193" s="13"/>
-      <c r="Q193" s="13"/>
-      <c r="R193" s="6"/>
-      <c r="S193" s="6"/>
-      <c r="T193" s="6"/>
-      <c r="U193" s="6"/>
-      <c r="V193" s="6"/>
-      <c r="W193" s="6"/>
+    <row r="193" ht="22.5" customHeight="1">
+      <c r="A193" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B193" s="8">
+        <v>46236.85738425926</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F193" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H193" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="I193" s="3">
+        <v>97.47</v>
+      </c>
+      <c r="J193" s="3">
+        <v>97.44</v>
+      </c>
+      <c r="K193" s="3">
+        <v>97.46</v>
+      </c>
+      <c r="L193" s="3">
+        <v>97.46</v>
+      </c>
+      <c r="M193" s="3">
+        <v>97.69</v>
+      </c>
+      <c r="N193" s="4">
+        <v>422.0</v>
+      </c>
+      <c r="O193" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="P193" s="4">
+        <v>13.0</v>
+      </c>
+      <c r="Q193" s="4">
+        <v>461.0</v>
+      </c>
+      <c r="R193" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S193" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T193" s="11"/>
+      <c r="U193" s="11"/>
+      <c r="V193" s="9"/>
+      <c r="W193" s="9"/>
       <c r="X193" s="6"/>
       <c r="Y193" s="6"/>
       <c r="Z193" s="6"/>
@@ -14627,30 +14994,68 @@
       <c r="AE193" s="6"/>
       <c r="AF193" s="6"/>
     </row>
-    <row r="194">
-      <c r="A194" s="12"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="12"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="12"/>
-      <c r="I194" s="13"/>
-      <c r="J194" s="13"/>
-      <c r="K194" s="13"/>
-      <c r="L194" s="13"/>
-      <c r="M194" s="13"/>
-      <c r="N194" s="13"/>
-      <c r="O194" s="13"/>
-      <c r="P194" s="13"/>
-      <c r="Q194" s="13"/>
-      <c r="R194" s="6"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
+    <row r="194" ht="22.5" customHeight="1">
+      <c r="A194" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B194" s="8">
+        <v>46236.88182870371</v>
+      </c>
+      <c r="C194" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="I194" s="3">
+        <v>95.15</v>
+      </c>
+      <c r="J194" s="3">
+        <v>95.12</v>
+      </c>
+      <c r="K194" s="3">
+        <v>95.13</v>
+      </c>
+      <c r="L194" s="3">
+        <v>95.14</v>
+      </c>
+      <c r="M194" s="3">
+        <v>95.37</v>
+      </c>
+      <c r="N194" s="4">
+        <v>412.0</v>
+      </c>
+      <c r="O194" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="P194" s="4">
+        <v>24.0</v>
+      </c>
+      <c r="Q194" s="4">
+        <v>450.0</v>
+      </c>
+      <c r="R194" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S194" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T194" s="11"/>
+      <c r="U194" s="11"/>
+      <c r="V194" s="9"/>
+      <c r="W194" s="9"/>
       <c r="X194" s="6"/>
       <c r="Y194" s="6"/>
       <c r="Z194" s="6"/>
@@ -14661,30 +15066,68 @@
       <c r="AE194" s="6"/>
       <c r="AF194" s="6"/>
     </row>
-    <row r="195">
-      <c r="A195" s="12"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="12"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="12"/>
-      <c r="I195" s="13"/>
-      <c r="J195" s="13"/>
-      <c r="K195" s="13"/>
-      <c r="L195" s="13"/>
-      <c r="M195" s="13"/>
-      <c r="N195" s="13"/>
-      <c r="O195" s="13"/>
-      <c r="P195" s="13"/>
-      <c r="Q195" s="13"/>
-      <c r="R195" s="6"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
+    <row r="195" ht="22.5" customHeight="1">
+      <c r="A195" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B195" s="8">
+        <v>46236.88282407408</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F195" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="I195" s="3">
+        <v>97.8</v>
+      </c>
+      <c r="J195" s="3">
+        <v>97.78</v>
+      </c>
+      <c r="K195" s="3">
+        <v>97.79</v>
+      </c>
+      <c r="L195" s="3">
+        <v>97.79</v>
+      </c>
+      <c r="M195" s="3">
+        <v>97.92</v>
+      </c>
+      <c r="N195" s="4">
+        <v>423.0</v>
+      </c>
+      <c r="O195" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="P195" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="Q195" s="4">
+        <v>463.0</v>
+      </c>
+      <c r="R195" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S195" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="T195" s="11"/>
+      <c r="U195" s="11"/>
+      <c r="V195" s="9"/>
+      <c r="W195" s="9"/>
       <c r="X195" s="6"/>
       <c r="Y195" s="6"/>
       <c r="Z195" s="6"/>
@@ -48456,6 +48899,346 @@
       <c r="AD1188" s="6"/>
       <c r="AE1188" s="6"/>
       <c r="AF1188" s="6"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="12"/>
+      <c r="B1189" s="6"/>
+      <c r="C1189" s="6"/>
+      <c r="D1189" s="6"/>
+      <c r="E1189" s="6"/>
+      <c r="F1189" s="12"/>
+      <c r="G1189" s="12"/>
+      <c r="H1189" s="12"/>
+      <c r="I1189" s="13"/>
+      <c r="J1189" s="13"/>
+      <c r="K1189" s="13"/>
+      <c r="L1189" s="13"/>
+      <c r="M1189" s="13"/>
+      <c r="N1189" s="13"/>
+      <c r="O1189" s="13"/>
+      <c r="P1189" s="13"/>
+      <c r="Q1189" s="13"/>
+      <c r="R1189" s="6"/>
+      <c r="S1189" s="6"/>
+      <c r="T1189" s="6"/>
+      <c r="U1189" s="6"/>
+      <c r="V1189" s="6"/>
+      <c r="W1189" s="6"/>
+      <c r="X1189" s="6"/>
+      <c r="Y1189" s="6"/>
+      <c r="Z1189" s="6"/>
+      <c r="AA1189" s="6"/>
+      <c r="AB1189" s="6"/>
+      <c r="AC1189" s="6"/>
+      <c r="AD1189" s="6"/>
+      <c r="AE1189" s="6"/>
+      <c r="AF1189" s="6"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="12"/>
+      <c r="B1190" s="6"/>
+      <c r="C1190" s="6"/>
+      <c r="D1190" s="6"/>
+      <c r="E1190" s="6"/>
+      <c r="F1190" s="12"/>
+      <c r="G1190" s="12"/>
+      <c r="H1190" s="12"/>
+      <c r="I1190" s="13"/>
+      <c r="J1190" s="13"/>
+      <c r="K1190" s="13"/>
+      <c r="L1190" s="13"/>
+      <c r="M1190" s="13"/>
+      <c r="N1190" s="13"/>
+      <c r="O1190" s="13"/>
+      <c r="P1190" s="13"/>
+      <c r="Q1190" s="13"/>
+      <c r="R1190" s="6"/>
+      <c r="S1190" s="6"/>
+      <c r="T1190" s="6"/>
+      <c r="U1190" s="6"/>
+      <c r="V1190" s="6"/>
+      <c r="W1190" s="6"/>
+      <c r="X1190" s="6"/>
+      <c r="Y1190" s="6"/>
+      <c r="Z1190" s="6"/>
+      <c r="AA1190" s="6"/>
+      <c r="AB1190" s="6"/>
+      <c r="AC1190" s="6"/>
+      <c r="AD1190" s="6"/>
+      <c r="AE1190" s="6"/>
+      <c r="AF1190" s="6"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="12"/>
+      <c r="B1191" s="6"/>
+      <c r="C1191" s="6"/>
+      <c r="D1191" s="6"/>
+      <c r="E1191" s="6"/>
+      <c r="F1191" s="12"/>
+      <c r="G1191" s="12"/>
+      <c r="H1191" s="12"/>
+      <c r="I1191" s="13"/>
+      <c r="J1191" s="13"/>
+      <c r="K1191" s="13"/>
+      <c r="L1191" s="13"/>
+      <c r="M1191" s="13"/>
+      <c r="N1191" s="13"/>
+      <c r="O1191" s="13"/>
+      <c r="P1191" s="13"/>
+      <c r="Q1191" s="13"/>
+      <c r="R1191" s="6"/>
+      <c r="S1191" s="6"/>
+      <c r="T1191" s="6"/>
+      <c r="U1191" s="6"/>
+      <c r="V1191" s="6"/>
+      <c r="W1191" s="6"/>
+      <c r="X1191" s="6"/>
+      <c r="Y1191" s="6"/>
+      <c r="Z1191" s="6"/>
+      <c r="AA1191" s="6"/>
+      <c r="AB1191" s="6"/>
+      <c r="AC1191" s="6"/>
+      <c r="AD1191" s="6"/>
+      <c r="AE1191" s="6"/>
+      <c r="AF1191" s="6"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="12"/>
+      <c r="B1192" s="6"/>
+      <c r="C1192" s="6"/>
+      <c r="D1192" s="6"/>
+      <c r="E1192" s="6"/>
+      <c r="F1192" s="12"/>
+      <c r="G1192" s="12"/>
+      <c r="H1192" s="12"/>
+      <c r="I1192" s="13"/>
+      <c r="J1192" s="13"/>
+      <c r="K1192" s="13"/>
+      <c r="L1192" s="13"/>
+      <c r="M1192" s="13"/>
+      <c r="N1192" s="13"/>
+      <c r="O1192" s="13"/>
+      <c r="P1192" s="13"/>
+      <c r="Q1192" s="13"/>
+      <c r="R1192" s="6"/>
+      <c r="S1192" s="6"/>
+      <c r="T1192" s="6"/>
+      <c r="U1192" s="6"/>
+      <c r="V1192" s="6"/>
+      <c r="W1192" s="6"/>
+      <c r="X1192" s="6"/>
+      <c r="Y1192" s="6"/>
+      <c r="Z1192" s="6"/>
+      <c r="AA1192" s="6"/>
+      <c r="AB1192" s="6"/>
+      <c r="AC1192" s="6"/>
+      <c r="AD1192" s="6"/>
+      <c r="AE1192" s="6"/>
+      <c r="AF1192" s="6"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="12"/>
+      <c r="B1193" s="6"/>
+      <c r="C1193" s="6"/>
+      <c r="D1193" s="6"/>
+      <c r="E1193" s="6"/>
+      <c r="F1193" s="12"/>
+      <c r="G1193" s="12"/>
+      <c r="H1193" s="12"/>
+      <c r="I1193" s="13"/>
+      <c r="J1193" s="13"/>
+      <c r="K1193" s="13"/>
+      <c r="L1193" s="13"/>
+      <c r="M1193" s="13"/>
+      <c r="N1193" s="13"/>
+      <c r="O1193" s="13"/>
+      <c r="P1193" s="13"/>
+      <c r="Q1193" s="13"/>
+      <c r="R1193" s="6"/>
+      <c r="S1193" s="6"/>
+      <c r="T1193" s="6"/>
+      <c r="U1193" s="6"/>
+      <c r="V1193" s="6"/>
+      <c r="W1193" s="6"/>
+      <c r="X1193" s="6"/>
+      <c r="Y1193" s="6"/>
+      <c r="Z1193" s="6"/>
+      <c r="AA1193" s="6"/>
+      <c r="AB1193" s="6"/>
+      <c r="AC1193" s="6"/>
+      <c r="AD1193" s="6"/>
+      <c r="AE1193" s="6"/>
+      <c r="AF1193" s="6"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="12"/>
+      <c r="B1194" s="6"/>
+      <c r="C1194" s="6"/>
+      <c r="D1194" s="6"/>
+      <c r="E1194" s="6"/>
+      <c r="F1194" s="12"/>
+      <c r="G1194" s="12"/>
+      <c r="H1194" s="12"/>
+      <c r="I1194" s="13"/>
+      <c r="J1194" s="13"/>
+      <c r="K1194" s="13"/>
+      <c r="L1194" s="13"/>
+      <c r="M1194" s="13"/>
+      <c r="N1194" s="13"/>
+      <c r="O1194" s="13"/>
+      <c r="P1194" s="13"/>
+      <c r="Q1194" s="13"/>
+      <c r="R1194" s="6"/>
+      <c r="S1194" s="6"/>
+      <c r="T1194" s="6"/>
+      <c r="U1194" s="6"/>
+      <c r="V1194" s="6"/>
+      <c r="W1194" s="6"/>
+      <c r="X1194" s="6"/>
+      <c r="Y1194" s="6"/>
+      <c r="Z1194" s="6"/>
+      <c r="AA1194" s="6"/>
+      <c r="AB1194" s="6"/>
+      <c r="AC1194" s="6"/>
+      <c r="AD1194" s="6"/>
+      <c r="AE1194" s="6"/>
+      <c r="AF1194" s="6"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="12"/>
+      <c r="B1195" s="6"/>
+      <c r="C1195" s="6"/>
+      <c r="D1195" s="6"/>
+      <c r="E1195" s="6"/>
+      <c r="F1195" s="12"/>
+      <c r="G1195" s="12"/>
+      <c r="H1195" s="12"/>
+      <c r="I1195" s="13"/>
+      <c r="J1195" s="13"/>
+      <c r="K1195" s="13"/>
+      <c r="L1195" s="13"/>
+      <c r="M1195" s="13"/>
+      <c r="N1195" s="13"/>
+      <c r="O1195" s="13"/>
+      <c r="P1195" s="13"/>
+      <c r="Q1195" s="13"/>
+      <c r="R1195" s="6"/>
+      <c r="S1195" s="6"/>
+      <c r="T1195" s="6"/>
+      <c r="U1195" s="6"/>
+      <c r="V1195" s="6"/>
+      <c r="W1195" s="6"/>
+      <c r="X1195" s="6"/>
+      <c r="Y1195" s="6"/>
+      <c r="Z1195" s="6"/>
+      <c r="AA1195" s="6"/>
+      <c r="AB1195" s="6"/>
+      <c r="AC1195" s="6"/>
+      <c r="AD1195" s="6"/>
+      <c r="AE1195" s="6"/>
+      <c r="AF1195" s="6"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="12"/>
+      <c r="B1196" s="6"/>
+      <c r="C1196" s="6"/>
+      <c r="D1196" s="6"/>
+      <c r="E1196" s="6"/>
+      <c r="F1196" s="12"/>
+      <c r="G1196" s="12"/>
+      <c r="H1196" s="12"/>
+      <c r="I1196" s="13"/>
+      <c r="J1196" s="13"/>
+      <c r="K1196" s="13"/>
+      <c r="L1196" s="13"/>
+      <c r="M1196" s="13"/>
+      <c r="N1196" s="13"/>
+      <c r="O1196" s="13"/>
+      <c r="P1196" s="13"/>
+      <c r="Q1196" s="13"/>
+      <c r="R1196" s="6"/>
+      <c r="S1196" s="6"/>
+      <c r="T1196" s="6"/>
+      <c r="U1196" s="6"/>
+      <c r="V1196" s="6"/>
+      <c r="W1196" s="6"/>
+      <c r="X1196" s="6"/>
+      <c r="Y1196" s="6"/>
+      <c r="Z1196" s="6"/>
+      <c r="AA1196" s="6"/>
+      <c r="AB1196" s="6"/>
+      <c r="AC1196" s="6"/>
+      <c r="AD1196" s="6"/>
+      <c r="AE1196" s="6"/>
+      <c r="AF1196" s="6"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="12"/>
+      <c r="B1197" s="6"/>
+      <c r="C1197" s="6"/>
+      <c r="D1197" s="6"/>
+      <c r="E1197" s="6"/>
+      <c r="F1197" s="12"/>
+      <c r="G1197" s="12"/>
+      <c r="H1197" s="12"/>
+      <c r="I1197" s="13"/>
+      <c r="J1197" s="13"/>
+      <c r="K1197" s="13"/>
+      <c r="L1197" s="13"/>
+      <c r="M1197" s="13"/>
+      <c r="N1197" s="13"/>
+      <c r="O1197" s="13"/>
+      <c r="P1197" s="13"/>
+      <c r="Q1197" s="13"/>
+      <c r="R1197" s="6"/>
+      <c r="S1197" s="6"/>
+      <c r="T1197" s="6"/>
+      <c r="U1197" s="6"/>
+      <c r="V1197" s="6"/>
+      <c r="W1197" s="6"/>
+      <c r="X1197" s="6"/>
+      <c r="Y1197" s="6"/>
+      <c r="Z1197" s="6"/>
+      <c r="AA1197" s="6"/>
+      <c r="AB1197" s="6"/>
+      <c r="AC1197" s="6"/>
+      <c r="AD1197" s="6"/>
+      <c r="AE1197" s="6"/>
+      <c r="AF1197" s="6"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="12"/>
+      <c r="B1198" s="6"/>
+      <c r="C1198" s="6"/>
+      <c r="D1198" s="6"/>
+      <c r="E1198" s="6"/>
+      <c r="F1198" s="12"/>
+      <c r="G1198" s="12"/>
+      <c r="H1198" s="12"/>
+      <c r="I1198" s="13"/>
+      <c r="J1198" s="13"/>
+      <c r="K1198" s="13"/>
+      <c r="L1198" s="13"/>
+      <c r="M1198" s="13"/>
+      <c r="N1198" s="13"/>
+      <c r="O1198" s="13"/>
+      <c r="P1198" s="13"/>
+      <c r="Q1198" s="13"/>
+      <c r="R1198" s="6"/>
+      <c r="S1198" s="6"/>
+      <c r="T1198" s="6"/>
+      <c r="U1198" s="6"/>
+      <c r="V1198" s="6"/>
+      <c r="W1198" s="6"/>
+      <c r="X1198" s="6"/>
+      <c r="Y1198" s="6"/>
+      <c r="Z1198" s="6"/>
+      <c r="AA1198" s="6"/>
+      <c r="AB1198" s="6"/>
+      <c r="AC1198" s="6"/>
+      <c r="AD1198" s="6"/>
+      <c r="AE1198" s="6"/>
+      <c r="AF1198" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -48643,10 +49426,20 @@
     <hyperlink r:id="rId182" ref="F183"/>
     <hyperlink r:id="rId183" ref="F184"/>
     <hyperlink r:id="rId184" ref="F185"/>
+    <hyperlink r:id="rId185" ref="F186"/>
+    <hyperlink r:id="rId186" ref="F187"/>
+    <hyperlink r:id="rId187" ref="F188"/>
+    <hyperlink r:id="rId188" ref="F189"/>
+    <hyperlink r:id="rId189" ref="F190"/>
+    <hyperlink r:id="rId190" ref="F191"/>
+    <hyperlink r:id="rId191" ref="F192"/>
+    <hyperlink r:id="rId192" ref="F193"/>
+    <hyperlink r:id="rId193" ref="F194"/>
+    <hyperlink r:id="rId194" ref="F195"/>
   </hyperlinks>
-  <drawing r:id="rId185"/>
+  <drawing r:id="rId195"/>
   <tableParts count="1">
-    <tablePart r:id="rId187"/>
+    <tablePart r:id="rId197"/>
   </tableParts>
 </worksheet>
 </file>
--- a/assets/SciClaimEval26_Results.xlsx
+++ b/assets/SciClaimEval26_Results.xlsx
@@ -2294,13 +2294,13 @@
     <col customWidth="1" min="4" max="4" width="14.75"/>
     <col customWidth="1" min="6" max="6" width="10.13"/>
     <col customWidth="1" min="7" max="7" width="12.5"/>
-    <col customWidth="1" min="8" max="8" width="24.38"/>
+    <col customWidth="1" min="8" max="8" width="30.13"/>
     <col customWidth="1" min="9" max="9" width="9.75"/>
     <col customWidth="1" min="10" max="12" width="13.0"/>
     <col customWidth="1" min="13" max="13" width="12.75"/>
     <col customWidth="1" min="14" max="17" width="7.25"/>
     <col customWidth="1" min="18" max="19" width="15.88"/>
-    <col customWidth="1" min="20" max="20" width="16.0"/>
+    <col customWidth="1" min="20" max="20" width="42.75"/>
     <col customWidth="1" min="21" max="21" width="12.25"/>
     <col customWidth="1" min="22" max="22" width="9.25"/>
     <col customWidth="1" min="23" max="23" width="45.0"/>
@@ -10454,7 +10454,7 @@
         <v>414</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H127" s="7" t="s">
         <v>415</v>
@@ -10528,7 +10528,7 @@
         <v>418</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H128" s="7" t="s">
         <v>419</v>
@@ -10602,7 +10602,7 @@
         <v>422</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H129" s="7" t="s">
         <v>423</v>
@@ -10996,7 +10996,7 @@
         <v>442</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H135" s="7" t="s">
         <v>443</v>
@@ -11070,7 +11070,7 @@
         <v>446</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H136" s="7" t="s">
         <v>447</v>
@@ -11144,7 +11144,7 @@
         <v>450</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H137" s="7" t="s">
         <v>451</v>
@@ -11218,7 +11218,7 @@
         <v>454</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H138" s="7" t="s">
         <v>455</v>
@@ -11292,7 +11292,7 @@
         <v>457</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H139" s="7" t="s">
         <v>458</v>
@@ -11478,7 +11478,7 @@
         <v>466</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H142" s="7" t="s">
         <v>467</v>
@@ -11552,7 +11552,7 @@
         <v>469</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H143" s="7" t="s">
         <v>470</v>
@@ -11626,7 +11626,7 @@
         <v>472</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H144" s="7" t="s">
         <v>473</v>
@@ -11814,7 +11814,7 @@
         <v>482</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H147" s="7" t="s">
         <v>483</v>
@@ -12076,7 +12076,7 @@
         <v>496</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H151" s="7" t="s">
         <v>497</v>
@@ -12150,7 +12150,7 @@
         <v>499</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H152" s="7" t="s">
         <v>500</v>
@@ -12224,7 +12224,7 @@
         <v>502</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="H153" s="7" t="s">
         <v>503</v>

--- a/assets/SciClaimEval26_Results.xlsx
+++ b/assets/SciClaimEval26_Results.xlsx
@@ -2292,7 +2292,7 @@
     <col customWidth="1" min="1" max="1" width="8.75"/>
     <col customWidth="1" min="2" max="2" width="17.13"/>
     <col customWidth="1" min="4" max="4" width="14.75"/>
-    <col customWidth="1" min="6" max="6" width="10.13"/>
+    <col customWidth="1" min="6" max="6" width="61.25"/>
     <col customWidth="1" min="7" max="7" width="12.5"/>
     <col customWidth="1" min="8" max="8" width="30.13"/>
     <col customWidth="1" min="9" max="9" width="9.75"/>
@@ -10010,7 +10010,7 @@
         <v>392</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>393</v>
